--- a/datos/ListaExcel/ListaPersonas1.xlsx
+++ b/datos/ListaExcel/ListaPersonas1.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/mmm1059_alu_ubu_es/Documents/Escritorio/TFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="8_{1358C022-85BE-4B7F-BF4E-FCC1DD1B9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01105BC7-A390-4A53-A263-F602E3D5E9EA}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{1358C022-85BE-4B7F-BF4E-FCC1DD1B9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48110DBD-793B-4F99-BB9D-F15CFE734530}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{B0B6A5FC-CE1B-471C-8D49-49C1E4593AB9}"/>
+    <workbookView xWindow="1848" yWindow="1848" windowWidth="10164" windowHeight="9780" xr2:uid="{B0B6A5FC-CE1B-471C-8D49-49C1E4593AB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
     <sheet name="HojaN" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,97 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="66">
+  <si>
+    <t>Columna3</t>
+  </si>
+  <si>
+    <t>Columna4</t>
+  </si>
+  <si>
+    <t>Columna5</t>
+  </si>
+  <si>
+    <t>Columna6</t>
+  </si>
+  <si>
+    <t>Columna7</t>
+  </si>
+  <si>
+    <t>Columna8</t>
+  </si>
+  <si>
+    <t>Columna9</t>
+  </si>
+  <si>
+    <t>Columna10</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>Marina</t>
+  </si>
+  <si>
+    <t>Alvaro</t>
+  </si>
+  <si>
+    <t>Carmen</t>
+  </si>
+  <si>
+    <t>PaulaChh</t>
+  </si>
+  <si>
+    <t>Paula</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>Rocio</t>
+  </si>
+  <si>
+    <t>Alba</t>
+  </si>
+  <si>
+    <t>Elena Uni</t>
+  </si>
+  <si>
+    <t>Marina Uni</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>DÍA 1</t>
+  </si>
+  <si>
+    <t>Lola Abu</t>
+  </si>
+  <si>
+    <t>Silvia</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Paula Marcos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo </t>
+  </si>
+  <si>
+    <t>Esther</t>
+  </si>
+  <si>
+    <t>Ruth</t>
+  </si>
+  <si>
+    <t>Isma</t>
+  </si>
   <si>
     <t>Sujeto</t>
   </si>
@@ -48,187 +138,103 @@
     <t>Peso (kg)</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mal </t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Bien pero poco</t>
+  </si>
+  <si>
+    <t>Gabina</t>
+  </si>
+  <si>
+    <t>Tania</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>IMC</t>
+  </si>
+  <si>
     <t>Altura (m)</t>
   </si>
   <si>
-    <t>IMC</t>
-  </si>
-  <si>
-    <t>Sexo</t>
+    <t>Jaime</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Qué tal ha dormido</t>
   </si>
   <si>
     <t>Fecha prueba 1</t>
   </si>
   <si>
-    <t xml:space="preserve"> Qué tal ha dormido</t>
-  </si>
-  <si>
     <t>Fecha prueba 2</t>
   </si>
   <si>
-    <t>Marina</t>
-  </si>
-  <si>
-    <t>Femenino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mal </t>
-  </si>
-  <si>
-    <t>Alvaro</t>
-  </si>
-  <si>
-    <t>Masculino</t>
-  </si>
-  <si>
-    <t>Regular</t>
+    <t>Muy bien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bien </t>
+  </si>
+  <si>
+    <t>Bien</t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>Rebeca</t>
+  </si>
+  <si>
+    <t>Pablo</t>
   </si>
   <si>
     <t>PaulaMunoa</t>
   </si>
   <si>
-    <t>Carmen</t>
-  </si>
-  <si>
-    <t>Bien</t>
-  </si>
-  <si>
-    <t>Paula</t>
-  </si>
-  <si>
-    <t>Bien pero poco</t>
-  </si>
-  <si>
-    <t>Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bien </t>
-  </si>
-  <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t>Muy bien</t>
-  </si>
-  <si>
-    <t>Jaime</t>
-  </si>
-  <si>
-    <t>Javier</t>
-  </si>
-  <si>
-    <t>Ana</t>
-  </si>
-  <si>
-    <t>Julio</t>
-  </si>
-  <si>
-    <t>Silvia</t>
-  </si>
-  <si>
     <t>Felix</t>
   </si>
   <si>
-    <t>Rebeca</t>
-  </si>
-  <si>
-    <t>Pablo</t>
-  </si>
-  <si>
-    <t>Esther</t>
-  </si>
-  <si>
-    <t>Rocio</t>
+    <t>Dolores</t>
   </si>
   <si>
     <t>Lucia</t>
   </si>
   <si>
-    <t>Tania</t>
-  </si>
-  <si>
-    <t>Maria</t>
-  </si>
-  <si>
-    <t>NOMBRE</t>
-  </si>
-  <si>
-    <t>DÍA 1</t>
-  </si>
-  <si>
-    <t>Columna3</t>
-  </si>
-  <si>
-    <t>Columna4</t>
-  </si>
-  <si>
-    <t>Columna5</t>
-  </si>
-  <si>
-    <t>Columna6</t>
-  </si>
-  <si>
-    <t>Columna7</t>
-  </si>
-  <si>
-    <t>Columna8</t>
-  </si>
-  <si>
-    <t>Columna9</t>
-  </si>
-  <si>
-    <t>Columna10</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>PaulaChh</t>
-  </si>
-  <si>
-    <t>Lola Abu</t>
-  </si>
-  <si>
-    <t>Alba</t>
-  </si>
-  <si>
-    <t>Elena Uni</t>
-  </si>
-  <si>
-    <t>Marina Uni</t>
-  </si>
-  <si>
-    <t>Juan</t>
-  </si>
-  <si>
-    <t>Paula Marcos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pablo </t>
-  </si>
-  <si>
-    <t>Ruth</t>
-  </si>
-  <si>
-    <t>Isma</t>
-  </si>
-  <si>
-    <t>Gabina</t>
-  </si>
-  <si>
-    <t>Dolores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angel </t>
+    <t xml:space="preserve">Maria </t>
+  </si>
+  <si>
+    <t>Angel</t>
   </si>
   <si>
     <t>Marimar</t>
   </si>
   <si>
+    <t>Roberto</t>
+  </si>
+  <si>
     <t>Azucena</t>
   </si>
   <si>
-    <t>Roberto</t>
+    <t>ElenaR</t>
+  </si>
+  <si>
+    <t>Ismael</t>
   </si>
 </sst>
 </file>
@@ -753,44 +759,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39EB97E4-5694-4C6C-9A99-36A159F56D33}">
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.109375" customWidth="1"/>
     <col min="8" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="K1" s="2"/>
     </row>
@@ -815,13 +821,13 @@
         <v>21.79930795847751</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H2" s="1">
         <v>45589</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -829,7 +835,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -845,13 +851,13 @@
         <v>25.469387755102041</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1">
         <v>45608</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -859,7 +865,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -875,13 +881,13 @@
         <v>19.948059768903612</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H4" s="1">
         <v>45609</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -889,7 +895,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>21</v>
@@ -905,13 +911,13 @@
         <v>24.840980089578082</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H5" s="1">
         <v>45610</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -919,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>21</v>
@@ -935,13 +941,13 @@
         <v>18.496498876998281</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H6" s="1">
         <v>45613</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J6" s="1">
         <v>45616</v>
@@ -952,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>26</v>
@@ -968,13 +974,13 @@
         <v>26.122448979591837</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1">
         <v>45614</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -982,7 +988,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>22</v>
@@ -998,13 +1004,13 @@
         <v>20.703124999999996</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H8" s="1">
         <v>45615</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1012,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -1028,13 +1034,13 @@
         <v>36.295922232041406</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H9" s="1">
         <v>45617</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1042,7 +1048,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>51</v>
@@ -1058,13 +1064,13 @@
         <v>24.111507464658473</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H10" s="1">
         <v>45629</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1072,7 +1078,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>46</v>
@@ -1088,13 +1094,13 @@
         <v>19.045073340238563</v>
       </c>
       <c r="G11" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H11" s="1">
         <v>45620</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -1102,7 +1108,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C12">
         <v>53</v>
@@ -1118,13 +1124,13 @@
         <v>27.77031263997133</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1">
         <v>45624</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1132,7 +1138,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13">
         <v>51</v>
@@ -1148,13 +1154,13 @@
         <v>21.230572023714146</v>
       </c>
       <c r="G13" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H13" s="1">
         <v>45625</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1162,7 +1168,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C14">
         <v>46</v>
@@ -1178,13 +1184,13 @@
         <v>25.059307026629689</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1">
         <v>45627</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1192,7 +1198,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C15">
         <v>47</v>
@@ -1204,17 +1210,17 @@
         <v>1.63</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" ref="F15:F26" si="1">D15/(E15*E15)</f>
+        <f>D15/(E15*E15)</f>
         <v>20.324438255109339</v>
       </c>
       <c r="G15" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H15" s="1">
         <v>45628</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1222,7 +1228,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>40</v>
@@ -1234,17 +1240,17 @@
         <v>1.83</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="1"/>
+        <f>D16/(E16*E16)</f>
         <v>20.603780345785182</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H16" s="1">
         <v>45633</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1252,7 +1258,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>38</v>
@@ -1264,17 +1270,17 @@
         <v>1.73</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="1"/>
+        <f>D17/(E17*E17)</f>
         <v>24.056934745564501</v>
       </c>
       <c r="G17" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H17" s="1">
         <v>45634</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1282,7 +1288,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <v>49</v>
@@ -1294,17 +1300,17 @@
         <v>1.69</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="1"/>
+        <f>D18/(E18*E18)</f>
         <v>28.010223731662059</v>
       </c>
       <c r="G18" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H18" s="1">
         <v>45635</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1312,29 +1318,23 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19">
+        <v>75</v>
+      </c>
+      <c r="D19">
+        <v>79</v>
+      </c>
+      <c r="E19">
+        <v>1.65</v>
+      </c>
+      <c r="F19" s="3">
+        <f>D19/(E19*E19)</f>
+        <v>29.017447199265384</v>
+      </c>
+      <c r="G19" t="s">
         <v>34</v>
-      </c>
-      <c r="C19">
-        <v>21</v>
-      </c>
-      <c r="D19">
-        <v>57</v>
-      </c>
-      <c r="E19">
-        <v>1.58</v>
-      </c>
-      <c r="F19" s="3">
-        <f t="shared" si="1"/>
-        <v>22.832879346258608</v>
-      </c>
-      <c r="G19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>45652</v>
-      </c>
-      <c r="I19" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1342,29 +1342,23 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C20">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D20">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E20">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="1"/>
-        <v>25.099501595611173</v>
+        <f t="shared" ref="F20:F29" si="1">D20/(E20*E20)</f>
+        <v>22.832879346258608</v>
       </c>
       <c r="G20" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>45653</v>
-      </c>
-      <c r="I20" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1372,7 +1366,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>35</v>
@@ -1388,13 +1382,7 @@
         <v>18.732782369146008</v>
       </c>
       <c r="G21" t="s">
-        <v>10</v>
-      </c>
-      <c r="H21" s="1">
-        <v>45654</v>
-      </c>
-      <c r="I21" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1402,29 +1390,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C22">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="D22">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" si="1"/>
-        <v>29.017447199265384</v>
+        <v>25.099501595611173</v>
       </c>
       <c r="G22" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>45664</v>
-      </c>
-      <c r="I22" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1448,13 +1430,7 @@
         <v>25.351541373715524</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="1">
-        <v>45671</v>
-      </c>
-      <c r="I23" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1478,13 +1454,7 @@
         <v>20.571428571428573</v>
       </c>
       <c r="G24" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="1">
-        <v>45672</v>
-      </c>
-      <c r="I24" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1492,7 +1462,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25">
         <v>51</v>
@@ -1508,13 +1478,7 @@
         <v>24.337479718766904</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="1">
-        <v>45673</v>
-      </c>
-      <c r="I25" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -1522,7 +1486,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26">
         <v>52</v>
@@ -1538,13 +1502,79 @@
         <v>23.624447492760247</v>
       </c>
       <c r="G26" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" s="1">
-        <v>45674</v>
-      </c>
-      <c r="I26" t="s">
-        <v>14</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>52</v>
+      </c>
+      <c r="E27">
+        <v>1.64</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="1"/>
+        <v>19.333729922665082</v>
+      </c>
+      <c r="G27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28">
+        <v>49</v>
+      </c>
+      <c r="D28">
+        <v>52</v>
+      </c>
+      <c r="E28">
+        <v>1.58</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="1"/>
+        <v>20.82999519307803</v>
+      </c>
+      <c r="G28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29">
+        <v>49</v>
+      </c>
+      <c r="D29">
+        <v>67</v>
+      </c>
+      <c r="E29">
+        <v>1.77</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="1"/>
+        <v>21.385936352899868</v>
+      </c>
+      <c r="G29" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1554,42 +1584,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF28CE65-45A0-45FF-84FE-9C8C064BABAA}">
-  <dimension ref="B3:K33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B3:K25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -1597,212 +1627,124 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/datos/ListaExcel/ListaPersonas1.xlsx
+++ b/datos/ListaExcel/ListaPersonas1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/mmm1059_alu_ubu_es/Documents/Escritorio/TFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/mmm1059_alu_ubu_es/Documents/Escritorio/TFG-Marina-Martin/datos/ListaExcel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{1358C022-85BE-4B7F-BF4E-FCC1DD1B9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48110DBD-793B-4F99-BB9D-F15CFE734530}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="8_{1358C022-85BE-4B7F-BF4E-FCC1DD1B9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA6B87B-CE25-44A0-9729-DAA8F01C110D}"/>
   <bookViews>
-    <workbookView xWindow="1848" yWindow="1848" windowWidth="10164" windowHeight="9780" xr2:uid="{B0B6A5FC-CE1B-471C-8D49-49C1E4593AB9}"/>
+    <workbookView xWindow="924" yWindow="1176" windowWidth="10164" windowHeight="9780" xr2:uid="{B0B6A5FC-CE1B-471C-8D49-49C1E4593AB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
@@ -36,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="72">
   <si>
     <t>Columna3</t>
   </si>
@@ -235,6 +257,24 @@
   </si>
   <si>
     <t>Ismael</t>
+  </si>
+  <si>
+    <t>Javito</t>
+  </si>
+  <si>
+    <t>Marijose</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>Niceto</t>
+  </si>
+  <si>
+    <t>Aner</t>
+  </si>
+  <si>
+    <t>Mikel</t>
   </si>
 </sst>
 </file>
@@ -417,10 +457,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -759,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39EB97E4-5694-4C6C-9A99-36A159F56D33}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -816,9 +852,9 @@
       <c r="E2">
         <v>1.7</v>
       </c>
-      <c r="F2" s="3">
-        <f>D2/(E2*E2)</f>
-        <v>21.79930795847751</v>
+      <c r="F2" s="3" cm="1">
+        <f t="array" aca="1" ref="F2" ca="1">D2/+F2:F25(E2*E2)</f>
+        <v>0</v>
       </c>
       <c r="G2" t="s">
         <v>34</v>
@@ -1354,7 +1390,7 @@
         <v>1.58</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" ref="F20:F29" si="1">D20/(E20*E20)</f>
+        <f t="shared" ref="F20:F35" si="1">D20/(E20*E20)</f>
         <v>22.832879346258608</v>
       </c>
       <c r="G20" t="s">
@@ -1574,6 +1610,141 @@
         <v>21.385936352899868</v>
       </c>
       <c r="G29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30">
+        <v>44</v>
+      </c>
+      <c r="D30">
+        <v>74</v>
+      </c>
+      <c r="E30">
+        <v>1.72</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="1"/>
+        <v>25.013520822065985</v>
+      </c>
+      <c r="G30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31">
+        <v>53</v>
+      </c>
+      <c r="D31">
+        <v>89</v>
+      </c>
+      <c r="E31">
+        <v>1.5</v>
+      </c>
+      <c r="F31" s="3">
+        <f>D31/(E31*E31)</f>
+        <v>39.555555555555557</v>
+      </c>
+      <c r="G31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32">
+        <v>53</v>
+      </c>
+      <c r="D32">
+        <v>96</v>
+      </c>
+      <c r="E32">
+        <v>1.68</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="1"/>
+        <v>34.013605442176875</v>
+      </c>
+      <c r="G32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33">
+        <v>56</v>
+      </c>
+      <c r="D33">
+        <v>110</v>
+      </c>
+      <c r="E33">
+        <v>1.85</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="1"/>
+        <v>32.140248356464568</v>
+      </c>
+      <c r="G33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34">
+        <v>21</v>
+      </c>
+      <c r="D34">
+        <v>102</v>
+      </c>
+      <c r="E34">
+        <v>1.86</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="1"/>
+        <v>29.483177245924381</v>
+      </c>
+      <c r="G34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="3" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G35" t="s">
         <v>35</v>
       </c>
     </row>

--- a/datos/ListaExcel/ListaPersonas1.xlsx
+++ b/datos/ListaExcel/ListaPersonas1.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/mmm1059_alu_ubu_es/Documents/Escritorio/TFG-Marina-Martin/datos/ListaExcel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="8_{1358C022-85BE-4B7F-BF4E-FCC1DD1B9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA6B87B-CE25-44A0-9729-DAA8F01C110D}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="8_{1358C022-85BE-4B7F-BF4E-FCC1DD1B9E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2761EEFA-EDC9-4F4C-872B-3C2C496CD890}"/>
   <bookViews>
-    <workbookView xWindow="924" yWindow="1176" windowWidth="10164" windowHeight="9780" xr2:uid="{B0B6A5FC-CE1B-471C-8D49-49C1E4593AB9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B0B6A5FC-CE1B-471C-8D49-49C1E4593AB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
     <sheet name="HojaN" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -457,6 +457,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1740,9 +1744,18 @@
       <c r="B35" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F35" s="3" t="e">
+      <c r="C35">
+        <v>21</v>
+      </c>
+      <c r="D35">
+        <v>80</v>
+      </c>
+      <c r="E35">
+        <v>1.74</v>
+      </c>
+      <c r="F35" s="3">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>26.423569824283259</v>
       </c>
       <c r="G35" t="s">
         <v>35</v>
